--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679383</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135679382</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679383</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135679382</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679383</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135679382</v>
       </c>
       <c r="B6" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679383</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135679382</v>
       </c>
       <c r="B6" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 642-2026 artfynd.xlsx
+++ b/artfynd/S 642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679383</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135679377</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135679379</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135679387</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135679382</v>
       </c>
       <c r="B6" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135679380</v>
       </c>
       <c r="B7" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
